--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5701B-5099-43D5-905B-E3FA9A53292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B18F1-A9CE-426E-BCD9-9DDA79F377D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>nombre</t>
   </si>
@@ -765,7 +765,9 @@
       <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="K6" s="3">
         <v>1</v>
       </c>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B18F1-A9CE-426E-BCD9-9DDA79F377D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8724AE-15B3-4C23-9A3B-120BC8FE203D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8724AE-15B3-4C23-9A3B-120BC8FE203D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8E5016-F203-4555-8465-00CDEE3CAD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>nombre</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Parallax</t>
+  </si>
+  <si>
+    <t>Darkseid</t>
   </si>
 </sst>
 </file>
@@ -652,7 +655,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="4" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K3" s="3">
         <v>1</v>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8E5016-F203-4555-8465-00CDEE3CAD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EECB32-C1A9-4FCB-901F-B99198F1D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="238">
   <si>
     <t>nombre</t>
   </si>
@@ -66,66 +66,9 @@
     <t>ID_evento</t>
   </si>
   <si>
-    <t>Fiebre de Esporas</t>
-  </si>
-  <si>
     <t>cartas</t>
   </si>
   <si>
-    <t>Derrota a Poison Ivy y obtén increibles recompensas.</t>
-  </si>
-  <si>
-    <t>Poison Ivy</t>
-  </si>
-  <si>
-    <t>Crisis en Tierras Infinitas</t>
-  </si>
-  <si>
-    <t>¡El Multiverso está en crisis! ¡Derrota a todos los villanos antes de que sea demasiado tarde!</t>
-  </si>
-  <si>
-    <t>Superboy Prime</t>
-  </si>
-  <si>
-    <t>Spectre</t>
-  </si>
-  <si>
-    <t>Antimonitor</t>
-  </si>
-  <si>
-    <t>Psycho-Pirate</t>
-  </si>
-  <si>
-    <t>La Furia de la Casa de EL</t>
-  </si>
-  <si>
-    <t>Enfréntate a los kryptonianos más poderosos del multiverso.</t>
-  </si>
-  <si>
-    <t>Birrazo ha llegado a la tierra. No permitas que cause más daños.</t>
-  </si>
-  <si>
-    <t>¿Ese es... Superman?</t>
-  </si>
-  <si>
-    <t>El Terror de Gotham</t>
-  </si>
-  <si>
-    <t>Nadie se atreve a meterse con la Bat-Familia. ¿Y tú?</t>
-  </si>
-  <si>
-    <t>Linternas Descontroladas</t>
-  </si>
-  <si>
-    <t>Los linternas de todo el universo crean el caos. ¡Ocúpate de ellos!</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Superboy</t>
-  </si>
-  <si>
     <t>Supergirl</t>
   </si>
   <si>
@@ -150,9 +93,6 @@
     <t>Red Hood</t>
   </si>
   <si>
-    <t>Cassandra Cain</t>
-  </si>
-  <si>
     <t>Batman</t>
   </si>
   <si>
@@ -165,10 +105,640 @@
     <t>Lyssa Drak</t>
   </si>
   <si>
-    <t>Parallax</t>
-  </si>
-  <si>
     <t>Darkseid</t>
+  </si>
+  <si>
+    <t>Incursión en la Atalaya</t>
+  </si>
+  <si>
+    <t>Enfréntate a los héroes más poderosos de la Tierra en una batalla masiva por el control de la Atalaya</t>
+  </si>
+  <si>
+    <t>Martian Manhunter</t>
+  </si>
+  <si>
+    <t>Cyborg</t>
+  </si>
+  <si>
+    <t>Hall Jordan</t>
+  </si>
+  <si>
+    <t>Wonder Woman</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>Los Caballeros de Gotham</t>
+  </si>
+  <si>
+    <t>La Bat-Family vigila Gotham. Sobrevive a emboscadas, gadgets y combates en los tejados de la ciudad más peligrosa de la Tierra.</t>
+  </si>
+  <si>
+    <t>Huntress</t>
+  </si>
+  <si>
+    <t>Fuerza de la velocidad</t>
+  </si>
+  <si>
+    <t>Los velocistas han fracturado la Fuerza de la velocidad. Resiste ataques imposibles de seguir a simple vista.</t>
+  </si>
+  <si>
+    <t>Vibe</t>
+  </si>
+  <si>
+    <t>Jay Garrick</t>
+  </si>
+  <si>
+    <t>Jesse Quick</t>
+  </si>
+  <si>
+    <t>Kid Flash</t>
+  </si>
+  <si>
+    <t>En los días más brillantes</t>
+  </si>
+  <si>
+    <t>El cuerpo de Linternas verdes ha rodeado la Tierra. Destruye sus constructos y derrota a los Lanterns antes del juicio final.</t>
+  </si>
+  <si>
+    <t>Arisia Rrab</t>
+  </si>
+  <si>
+    <t>Abin Sur</t>
+  </si>
+  <si>
+    <t>Kyle Rayner</t>
+  </si>
+  <si>
+    <t>Guy Gardner</t>
+  </si>
+  <si>
+    <t>Jessica Cruz</t>
+  </si>
+  <si>
+    <t>John Stewart</t>
+  </si>
+  <si>
+    <t>Indigo-1</t>
+  </si>
+  <si>
+    <t>Saint Walker</t>
+  </si>
+  <si>
+    <t>La luz de la esperanza</t>
+  </si>
+  <si>
+    <t>Brother Hymn</t>
+  </si>
+  <si>
+    <t>Brother Warth</t>
+  </si>
+  <si>
+    <t>Kyle Rayner (Blue Lantern)</t>
+  </si>
+  <si>
+    <t>Barry Allen (Blue Lantern)</t>
+  </si>
+  <si>
+    <t>Derrota a los linternas azules en un combate donde las emociones se sienten a flor de piel.</t>
+  </si>
+  <si>
+    <t>Sister Sercy</t>
+  </si>
+  <si>
+    <t>La furia de la tribu</t>
+  </si>
+  <si>
+    <t>Enfrentate a la tribu de los índigo lanterns y a su poderosa lider; Indigo-1</t>
+  </si>
+  <si>
+    <t>Kraven</t>
+  </si>
+  <si>
+    <t>Munk</t>
+  </si>
+  <si>
+    <t>Ray Palmer (Indigo)</t>
+  </si>
+  <si>
+    <t>Hijos del cuarto mundo</t>
+  </si>
+  <si>
+    <t>Guerreros divinos llegan desde Nueva Génesis. Enfréntate a dioses cósmicos y tecnología imposible.</t>
+  </si>
+  <si>
+    <t>Bekka</t>
+  </si>
+  <si>
+    <t>Orion</t>
+  </si>
+  <si>
+    <t>Highfather</t>
+  </si>
+  <si>
+    <t>Big Barda</t>
+  </si>
+  <si>
+    <t>Mister Miracle</t>
+  </si>
+  <si>
+    <t>Sombras del destino</t>
+  </si>
+  <si>
+    <t>Magos y entidades oscuras han invocado un campo de batalla sobrenatural lleno de maldiciones y demonios.</t>
+  </si>
+  <si>
+    <t>Amethyst</t>
+  </si>
+  <si>
+    <t>Raven</t>
+  </si>
+  <si>
+    <t>Madame Xanadu</t>
+  </si>
+  <si>
+    <t>Etrigan</t>
+  </si>
+  <si>
+    <t>Doctor Fate</t>
+  </si>
+  <si>
+    <t>John Constantine</t>
+  </si>
+  <si>
+    <t>Zatanna</t>
+  </si>
+  <si>
+    <t>Flechas en la oscuridad</t>
+  </si>
+  <si>
+    <t>El equipo Arrow domina las calles con tácticas de guerrilla, trampas y ataques coordinados.</t>
+  </si>
+  <si>
+    <t>Katana</t>
+  </si>
+  <si>
+    <t>Thea Queen</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Black Canary</t>
+  </si>
+  <si>
+    <t>Green Arrow</t>
+  </si>
+  <si>
+    <t>La ira del Verde</t>
+  </si>
+  <si>
+    <t>La naturaleza se rebela. Plantas gigantes y criaturas salvajes invaden el campo de batalla.</t>
+  </si>
+  <si>
+    <t>Metamorpho</t>
+  </si>
+  <si>
+    <t>Beast Boy</t>
+  </si>
+  <si>
+    <t>Vixen</t>
+  </si>
+  <si>
+    <t>Swamp Thing</t>
+  </si>
+  <si>
+    <t>Profundidades abisales</t>
+  </si>
+  <si>
+    <t>Las fuerzas atlantes atacan desde el océano. Combate bajo el agua contra los guerreros de Atlantis.</t>
+  </si>
+  <si>
+    <t>Atlanna</t>
+  </si>
+  <si>
+    <t>Aqualad</t>
+  </si>
+  <si>
+    <t>Mera</t>
+  </si>
+  <si>
+    <t>Aquaman</t>
+  </si>
+  <si>
+    <t>Campeonas del olimpo</t>
+  </si>
+  <si>
+    <t>Las amazonas desafían a cualquiera que ose enfrentarse a las guerreras de Temiscira.</t>
+  </si>
+  <si>
+    <t>Trinity</t>
+  </si>
+  <si>
+    <t>Yara Flor</t>
+  </si>
+  <si>
+    <t>Artemis</t>
+  </si>
+  <si>
+    <t>Nubia</t>
+  </si>
+  <si>
+    <t>Wonder Girl</t>
+  </si>
+  <si>
+    <t>Donna Troy</t>
+  </si>
+  <si>
+    <t>La Torre de los Titanes</t>
+  </si>
+  <si>
+    <t>Los jóvenes héroes luchan en equipo con ataques rápidos, poderes combinados y combate constante.</t>
+  </si>
+  <si>
+    <t>Omen</t>
+  </si>
+  <si>
+    <t>Bumblebee</t>
+  </si>
+  <si>
+    <t>Starfire</t>
+  </si>
+  <si>
+    <t>Héroes del futuro llegan al presente con tecnología avanzada y tácticas imposibles de predecir.</t>
+  </si>
+  <si>
+    <t>Héroes del Siglo XXXI</t>
+  </si>
+  <si>
+    <t>Brainiac-5</t>
+  </si>
+  <si>
+    <t>Shadow Lass</t>
+  </si>
+  <si>
+    <t>Lightning Lad</t>
+  </si>
+  <si>
+    <t>Cosmic Boy</t>
+  </si>
+  <si>
+    <t>Saturn Girl</t>
+  </si>
+  <si>
+    <t>Ciudad del crimen</t>
+  </si>
+  <si>
+    <t>Los peores criminales de Gotham han tomado la ciudad. Sobrevive al caos y derrota a los villanos más enfermizos.</t>
+  </si>
+  <si>
+    <t>Joker</t>
+  </si>
+  <si>
+    <t>Harley Quinn</t>
+  </si>
+  <si>
+    <t>Punchline</t>
+  </si>
+  <si>
+    <t>Bane</t>
+  </si>
+  <si>
+    <t>Two-Face</t>
+  </si>
+  <si>
+    <t>Riddler</t>
+  </si>
+  <si>
+    <t>Scarecrow</t>
+  </si>
+  <si>
+    <t>Sombras de guerra</t>
+  </si>
+  <si>
+    <t>Asesinos de élite acechan desde las sombras. Esquiva ataques letales y enfréntate a los mejores combatientes del mundo.</t>
+  </si>
+  <si>
+    <t>Assassin</t>
+  </si>
+  <si>
+    <t>Cheshire</t>
+  </si>
+  <si>
+    <t>Deadshot</t>
+  </si>
+  <si>
+    <t>Deathstroke</t>
+  </si>
+  <si>
+    <t>Lady Shiva</t>
+  </si>
+  <si>
+    <t>Talia al Ghul</t>
+  </si>
+  <si>
+    <t>Ra's al Ghul</t>
+  </si>
+  <si>
+    <t>Los enemigos de Flash atacan Central City usando armas congelantes, portales y velocidad extrema.</t>
+  </si>
+  <si>
+    <t>Velocidad corrupta</t>
+  </si>
+  <si>
+    <t>Captain Boomerang</t>
+  </si>
+  <si>
+    <t>Mirror Master</t>
+  </si>
+  <si>
+    <t>Heat Wave</t>
+  </si>
+  <si>
+    <t>Captain Cold</t>
+  </si>
+  <si>
+    <t>Zoom</t>
+  </si>
+  <si>
+    <t>Reverse Flash</t>
+  </si>
+  <si>
+    <t>El miedo domina el campo de batalla mientras el Sinestro Corps invade el sector terrestre.</t>
+  </si>
+  <si>
+    <t>Domina el miedo</t>
+  </si>
+  <si>
+    <t>Feena Sik</t>
+  </si>
+  <si>
+    <t>Arkillo</t>
+  </si>
+  <si>
+    <t>Sangre y fuego</t>
+  </si>
+  <si>
+    <t>Los Red Lanterns arrasan todo a su paso impulsados por una rabia imparable.</t>
+  </si>
+  <si>
+    <t>Rankorr</t>
+  </si>
+  <si>
+    <t>Guy Gardner (Red Lantern)</t>
+  </si>
+  <si>
+    <t>Zilius Zox</t>
+  </si>
+  <si>
+    <t>Skallox</t>
+  </si>
+  <si>
+    <t>Dex-Starr</t>
+  </si>
+  <si>
+    <t>Atrocitus</t>
+  </si>
+  <si>
+    <t>La noche más oscura</t>
+  </si>
+  <si>
+    <t>Los muertos regresan como Black Lanterns. Sobrevive al avance del ejército de Nekron.</t>
+  </si>
+  <si>
+    <t>Black Hand</t>
+  </si>
+  <si>
+    <t>Nekron</t>
+  </si>
+  <si>
+    <t>Las fuerzas de Apokolips invaden la Tierra. Enfréntate a dioses oscuros y oleadas de Parademons.</t>
+  </si>
+  <si>
+    <t>Darkseid ha llegado</t>
+  </si>
+  <si>
+    <t>Steppenwolf</t>
+  </si>
+  <si>
+    <t>DeSaad</t>
+  </si>
+  <si>
+    <t>Granny Goodness</t>
+  </si>
+  <si>
+    <t>Kalibak</t>
+  </si>
+  <si>
+    <t>Grail</t>
+  </si>
+  <si>
+    <t>Parademon</t>
+  </si>
+  <si>
+    <t>Stompa</t>
+  </si>
+  <si>
+    <t>Mad Harriet</t>
+  </si>
+  <si>
+    <t>Lashina</t>
+  </si>
+  <si>
+    <t>Bernadeth</t>
+  </si>
+  <si>
+    <t>Aurelie</t>
+  </si>
+  <si>
+    <t>Gilotina</t>
+  </si>
+  <si>
+    <t>Las Furias de Apokolips</t>
+  </si>
+  <si>
+    <t>Enfrentate a las villanas más temibles del universo y sobrevive a todas sus inesperadas estrategias de combate.</t>
+  </si>
+  <si>
+    <t>Dominación mundial</t>
+  </si>
+  <si>
+    <t>Los mayores genios y conquistadores del universo unen fuerzas en un combate que decidirá el destino de la humanidad.</t>
+  </si>
+  <si>
+    <t>Pyscho-Pirate</t>
+  </si>
+  <si>
+    <t>Telos</t>
+  </si>
+  <si>
+    <t>Maxwell Lord</t>
+  </si>
+  <si>
+    <t>Vandal Savage</t>
+  </si>
+  <si>
+    <t>Black Adam</t>
+  </si>
+  <si>
+    <t>Lex Luthor</t>
+  </si>
+  <si>
+    <t>Brainiac</t>
+  </si>
+  <si>
+    <t>La caída de Krypton</t>
+  </si>
+  <si>
+    <t>Guerreros kryptonianos desatan una batalla devastadora bajo la luz del sol amarillo de la Tierra.</t>
+  </si>
+  <si>
+    <t>Reign</t>
+  </si>
+  <si>
+    <t>Superboy-Prime</t>
+  </si>
+  <si>
+    <t>Ultraman</t>
+  </si>
+  <si>
+    <t>Faora</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Ursa</t>
+  </si>
+  <si>
+    <t>General Zod</t>
+  </si>
+  <si>
+    <t>Juicio final</t>
+  </si>
+  <si>
+    <t>Los enemigos más peligrosos de Superman atacan Metrópolis con fuerza devastadora.</t>
+  </si>
+  <si>
+    <t>The Eradicator</t>
+  </si>
+  <si>
+    <t>Superman Cyborg</t>
+  </si>
+  <si>
+    <t>Supergirl Cyborg</t>
+  </si>
+  <si>
+    <t>Parasite</t>
+  </si>
+  <si>
+    <t>Metallo</t>
+  </si>
+  <si>
+    <t>Doomsday</t>
+  </si>
+  <si>
+    <t>Profundidades oscuras</t>
+  </si>
+  <si>
+    <t>Los enemigos de Atlantis emergen del océano para dominar la superficie y a todos sus habitantes.</t>
+  </si>
+  <si>
+    <t>King Shark</t>
+  </si>
+  <si>
+    <t>Ocean Master</t>
+  </si>
+  <si>
+    <t>Black Manta</t>
+  </si>
+  <si>
+    <t>Infierno en la Tierra</t>
+  </si>
+  <si>
+    <t>Magia oscura y demonios convierten el combate en una auténtica pesadilla sobrenatural.</t>
+  </si>
+  <si>
+    <t>Brother Blood</t>
+  </si>
+  <si>
+    <t>Klarion</t>
+  </si>
+  <si>
+    <t>Deimos</t>
+  </si>
+  <si>
+    <t>Circe</t>
+  </si>
+  <si>
+    <t>Ares</t>
+  </si>
+  <si>
+    <t>Enchantress</t>
+  </si>
+  <si>
+    <t>Trigon</t>
+  </si>
+  <si>
+    <t>Los cinco temibles</t>
+  </si>
+  <si>
+    <t>Los enemigos de los Titanes atacan con tecnología, poderes psíquicos y fuerza bruta.</t>
+  </si>
+  <si>
+    <t>Arthur Light</t>
+  </si>
+  <si>
+    <t>Gizmo</t>
+  </si>
+  <si>
+    <t>Mammoth</t>
+  </si>
+  <si>
+    <t>Psimon</t>
+  </si>
+  <si>
+    <t>Jinx</t>
+  </si>
+  <si>
+    <t>Rebelión tecnológica</t>
+  </si>
+  <si>
+    <t>Robots, inteligencia artificial y tecnología experimental dominan el campo de batalla.</t>
+  </si>
+  <si>
+    <t>Ebon</t>
+  </si>
+  <si>
+    <t>Simon Stagg</t>
+  </si>
+  <si>
+    <t>Thinker</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Amazo</t>
+  </si>
+  <si>
+    <t>Multiverso oscuro</t>
+  </si>
+  <si>
+    <t>Versiones corruptas de Batman emergen del Multiverso Oscuro para destruir toda esperanza.</t>
+  </si>
+  <si>
+    <t>Dark Robin</t>
+  </si>
+  <si>
+    <t>Barbatos</t>
+  </si>
+  <si>
+    <t>Batman Who Laughs</t>
+  </si>
+  <si>
+    <t>Gorilla Grodd</t>
   </si>
 </sst>
 </file>
@@ -199,13 +769,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7C80"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFF9999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,26 +807,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -264,6 +829,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF9999"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -538,25 +1108,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="66.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" customWidth="1"/>
     <col min="12" max="12" width="17.28515625" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="33.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -597,230 +1168,1206 @@
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="6">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1</v>
+      </c>
+      <c r="M2" s="6">
+        <v>550</v>
+      </c>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
-        <v>100</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>600</v>
+      </c>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1</v>
+      </c>
+      <c r="L4" s="6">
+        <v>1</v>
+      </c>
+      <c r="M4" s="6">
+        <v>600</v>
+      </c>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="I5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="3">
-        <v>340</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2">
-        <v>340</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2">
         <v>1</v>
       </c>
       <c r="M5" s="2">
-        <v>100</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
+      <c r="B6" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="6">
+        <v>600</v>
+      </c>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="E7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="F7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2">
-        <v>340</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>500</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>500</v>
+      </c>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2">
-        <v>340</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>600</v>
+      </c>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6">
+        <v>600</v>
+      </c>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>550</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
+        <v>1</v>
+      </c>
+      <c r="M12" s="6">
+        <v>350</v>
+      </c>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>450</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6">
+        <v>600</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6">
+        <v>1</v>
+      </c>
+      <c r="M15" s="6">
+        <v>600</v>
+      </c>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>500</v>
+      </c>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6">
+        <v>1</v>
+      </c>
+      <c r="M17" s="6">
+        <v>600</v>
+      </c>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <v>600</v>
+      </c>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6">
+        <v>1</v>
+      </c>
+      <c r="M19" s="6">
+        <v>600</v>
+      </c>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2">
+        <v>500</v>
+      </c>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6">
+        <v>1</v>
+      </c>
+      <c r="M21" s="6">
+        <v>600</v>
+      </c>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>450</v>
+      </c>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6">
+        <v>1</v>
+      </c>
+      <c r="M23" s="6">
+        <v>600</v>
+      </c>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
+        <v>450</v>
+      </c>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6">
+        <v>1</v>
+      </c>
+      <c r="M25" s="6">
+        <v>600</v>
+      </c>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2">
+        <v>600</v>
+      </c>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="K27" s="6">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6">
+        <v>1</v>
+      </c>
+      <c r="M27" s="6">
+        <v>400</v>
+      </c>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2">
+        <v>600</v>
+      </c>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>27</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K29" s="6">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6">
+        <v>1</v>
+      </c>
+      <c r="M29" s="6">
+        <v>600</v>
+      </c>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2">
+        <v>550</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="K31" s="6">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6">
+        <v>1</v>
+      </c>
+      <c r="M31" s="6">
+        <v>450</v>
+      </c>
+      <c r="N31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EECB32-C1A9-4FCB-901F-B99198F1D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED0ED46-7E82-4A8B-B3AE-ACA228E89A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,9 +495,6 @@
     <t>Skallox</t>
   </si>
   <si>
-    <t>Dex-Starr</t>
-  </si>
-  <si>
     <t>Atrocitus</t>
   </si>
   <si>
@@ -739,6 +736,9 @@
   </si>
   <si>
     <t>Gorilla Grodd</t>
+  </si>
+  <si>
+    <t>Dex Starr</t>
   </si>
 </sst>
 </file>
@@ -1176,29 +1176,29 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K2" s="6">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>138</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>140</v>
@@ -1584,13 +1584,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -1598,7 +1598,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
@@ -1670,13 +1670,13 @@
         <v>155</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>24</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
@@ -1694,31 +1694,31 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -1774,28 +1774,28 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>26</v>
@@ -1858,31 +1858,31 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="D19" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="J19" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K19" s="6">
         <v>1</v>
@@ -1938,31 +1938,31 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="J21" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -2016,31 +2016,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -2094,31 +2094,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="J25" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
@@ -2178,23 +2178,23 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K27" s="6">
         <v>1</v>
@@ -2254,31 +2254,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="I29" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="J29" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="K29" s="6">
         <v>1</v>
@@ -2336,27 +2336,27 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K31" s="6">
         <v>1</v>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED0ED46-7E82-4A8B-B3AE-ACA228E89A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0645909-2867-447D-857D-1B48604EB6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0645909-2867-447D-857D-1B48604EB6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CEA91B-2D3D-492F-95EA-EEFD6EA73E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,9 +564,6 @@
     <t>Los mayores genios y conquistadores del universo unen fuerzas en un combate que decidirá el destino de la humanidad.</t>
   </si>
   <si>
-    <t>Pyscho-Pirate</t>
-  </si>
-  <si>
     <t>Telos</t>
   </si>
   <si>
@@ -594,9 +591,6 @@
     <t>Reign</t>
   </si>
   <si>
-    <t>Superboy-Prime</t>
-  </si>
-  <si>
     <t>Ultraman</t>
   </si>
   <si>
@@ -739,6 +733,12 @@
   </si>
   <si>
     <t>Dex Starr</t>
+  </si>
+  <si>
+    <t>Superboy Prime</t>
+  </si>
+  <si>
+    <t>Psycho-Pirate</t>
   </si>
 </sst>
 </file>
@@ -1176,29 +1176,29 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K2" s="6">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>138</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>140</v>
@@ -1670,7 +1670,7 @@
         <v>155</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>24</v>
@@ -1694,31 +1694,31 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="E15" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -1944,25 +1944,25 @@
         <v>178</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="J21" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -2016,31 +2016,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -2094,31 +2094,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
@@ -2178,23 +2178,23 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K27" s="6">
         <v>1</v>
@@ -2254,31 +2254,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="I29" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="J29" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="K29" s="6">
         <v>1</v>
@@ -2336,27 +2336,27 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K31" s="6">
         <v>1</v>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CEA91B-2D3D-492F-95EA-EEFD6EA73E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7F659-A1FC-41A0-9EA2-679C73C4B2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="239">
   <si>
     <t>nombre</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t>Psycho-Pirate</t>
+  </si>
+  <si>
+    <t>Hal Jordan</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>238</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>32</v>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7F659-A1FC-41A0-9EA2-679C73C4B2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF94C77-C833-46C1-B608-D25D5871CC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="238">
   <si>
     <t>nombre</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>Cyborg</t>
-  </si>
-  <si>
-    <t>Hall Jordan</t>
   </si>
   <si>
     <t>Wonder Woman</t>
@@ -1179,29 +1176,29 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2" s="6">
         <v>1</v>
@@ -1231,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>22</v>
@@ -1261,31 +1258,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
@@ -1303,10 +1300,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>19</v>
@@ -1324,7 +1321,7 @@
         <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>22</v>
@@ -1345,31 +1342,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -1387,27 +1384,27 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -1425,22 +1422,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>148</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -1463,31 +1460,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1505,31 +1502,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="K10" s="6">
         <v>1</v>
@@ -1547,29 +1544,29 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -1587,13 +1584,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -1601,7 +1598,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
@@ -1619,25 +1616,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
@@ -1655,31 +1652,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="H14" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>24</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
@@ -1697,31 +1694,31 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -1739,27 +1736,27 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
@@ -1777,28 +1774,28 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>26</v>
@@ -1819,31 +1816,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
@@ -1861,31 +1858,31 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>176</v>
-      </c>
       <c r="D19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>173</v>
-      </c>
       <c r="J19" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K19" s="6">
         <v>1</v>
@@ -1903,27 +1900,27 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
@@ -1941,31 +1938,31 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="J21" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -1983,25 +1980,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" s="2">
         <v>1</v>
@@ -2019,31 +2016,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -2061,25 +2058,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K24" s="2">
         <v>1</v>
@@ -2097,31 +2094,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="J25" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
@@ -2139,31 +2136,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K26" s="2">
         <v>1</v>
@@ -2181,23 +2178,23 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K27" s="6">
         <v>1</v>
@@ -2215,31 +2212,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
@@ -2257,31 +2254,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="I29" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="J29" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="K29" s="6">
         <v>1</v>
@@ -2299,25 +2296,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
@@ -2339,27 +2336,27 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K31" s="6">
         <v>1</v>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF94C77-C833-46C1-B608-D25D5871CC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AB95EB-B851-418B-8A0C-B550347A3E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="239">
   <si>
     <t>nombre</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t>Hal Jordan</t>
+  </si>
+  <si>
+    <t>tablero</t>
   </si>
 </sst>
 </file>
@@ -807,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -821,6 +824,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1108,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -1125,9 +1134,10 @@
     <col min="12" max="12" width="17.28515625" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="6.5703125" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1170,8 +1180,11 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>0</v>
       </c>
@@ -1210,8 +1223,9 @@
         <v>550</v>
       </c>
       <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1252,8 +1266,9 @@
         <v>600</v>
       </c>
       <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -1294,8 +1309,9 @@
         <v>600</v>
       </c>
       <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1336,8 +1352,9 @@
         <v>600</v>
       </c>
       <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -1378,8 +1395,9 @@
         <v>600</v>
       </c>
       <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1416,8 +1434,9 @@
         <v>500</v>
       </c>
       <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -1454,8 +1473,9 @@
         <v>500</v>
       </c>
       <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1496,8 +1516,9 @@
         <v>600</v>
       </c>
       <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -1538,8 +1559,9 @@
         <v>600</v>
       </c>
       <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1578,8 +1600,9 @@
         <v>550</v>
       </c>
       <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -1610,8 +1633,9 @@
         <v>350</v>
       </c>
       <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1646,8 +1670,9 @@
         <v>450</v>
       </c>
       <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -1688,8 +1713,9 @@
         <v>600</v>
       </c>
       <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -1730,8 +1756,9 @@
         <v>600</v>
       </c>
       <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1768,8 +1795,9 @@
         <v>500</v>
       </c>
       <c r="N16" s="4"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -1810,8 +1838,9 @@
         <v>600</v>
       </c>
       <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1852,8 +1881,9 @@
         <v>600</v>
       </c>
       <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -1894,8 +1924,9 @@
         <v>600</v>
       </c>
       <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1932,8 +1963,9 @@
         <v>500</v>
       </c>
       <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -1974,8 +2006,9 @@
         <v>600</v>
       </c>
       <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2010,8 +2043,9 @@
         <v>450</v>
       </c>
       <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -2052,8 +2086,9 @@
         <v>600</v>
       </c>
       <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2088,8 +2123,9 @@
         <v>450</v>
       </c>
       <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -2130,8 +2166,9 @@
         <v>600</v>
       </c>
       <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2172,8 +2209,9 @@
         <v>600</v>
       </c>
       <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="7"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -2206,8 +2244,9 @@
         <v>400</v>
       </c>
       <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2248,8 +2287,9 @@
         <v>600</v>
       </c>
       <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="7"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -2290,8 +2330,9 @@
         <v>600</v>
       </c>
       <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2330,8 +2371,9 @@
         <v>550</v>
       </c>
       <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -2368,6 +2410,7 @@
         <v>450</v>
       </c>
       <c r="N31" s="6"/>
+      <c r="O31" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/resources/eventos.xlsx
+++ b/public/resources/eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AB95EB-B851-418B-8A0C-B550347A3E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D2887E-E481-4BDA-B4C8-CF02D0E0C0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="240">
   <si>
     <t>nombre</t>
   </si>
@@ -742,6 +742,9 @@
   </si>
   <si>
     <t>tablero</t>
+  </si>
+  <si>
+    <t>Wally West</t>
   </si>
 </sst>
 </file>
@@ -2266,7 +2269,7 @@
         <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>74</v>
